--- a/pds_admin_WB/Backend/Backend/Result_Sheet_leg1.xlsx
+++ b/pds_admin_WB/Backend/Backend/Result_Sheet_leg1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
   <si>
     <t>Scenario</t>
   </si>
@@ -85,19 +85,16 @@
     <t>WestBengal</t>
   </si>
   <si>
-    <t>Paschim Bardhaman</t>
-  </si>
-  <si>
-    <t>Purba Bardhaman</t>
+    <t>Darjeeling</t>
+  </si>
+  <si>
+    <t>Howrah</t>
   </si>
   <si>
     <t>Kolkata</t>
   </si>
   <si>
-    <t>EF14003</t>
-  </si>
-  <si>
-    <t>EBDNFM1</t>
+    <t>abx</t>
   </si>
   <si>
     <t>Def</t>
@@ -112,6 +109,15 @@
     <t>Wholesale</t>
   </si>
   <si>
+    <t>AJOY NATH YADAV</t>
+  </si>
+  <si>
+    <t>Alipurduar</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
     <t>PR</t>
   </si>
   <si>
@@ -119,6 +125,9 @@
   </si>
   <si>
     <t>Atta</t>
+  </si>
+  <si>
+    <t>WheatR</t>
   </si>
 </sst>
 </file>
@@ -476,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -552,46 +561,46 @@
         <v>23</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>1182</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2">
-        <v>23.50248767</v>
+        <v>26.57895873</v>
       </c>
       <c r="I2">
-        <v>87.73095685</v>
+        <v>88.97369044</v>
       </c>
       <c r="J2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="K2">
-        <v>12</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
       <c r="M2" t="s">
         <v>22</v>
       </c>
       <c r="N2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="O2">
-        <v>23.50248767</v>
+        <v>22.573481</v>
       </c>
       <c r="P2">
-        <v>87.73095685</v>
+        <v>88.23092200000001</v>
       </c>
       <c r="Q2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R2">
-        <v>1222.15875</v>
+        <v>25</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>635.801</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -602,7 +611,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -610,47 +619,47 @@
       <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
-        <v>26</v>
+      <c r="F3">
+        <v>81</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3">
-        <v>23.474314</v>
+        <v>22.559808</v>
       </c>
       <c r="I3">
-        <v>87.70725899999999</v>
+        <v>88.30919969999999</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3" t="s">
         <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="O3">
-        <v>23.440923</v>
+        <v>22.573481</v>
       </c>
       <c r="P3">
-        <v>87.67574399999999</v>
+        <v>88.23092200000001</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R3">
-        <v>748.64</v>
+        <v>96</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>10.6225</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -661,55 +670,55 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>611</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>23.474314</v>
+        <v>22.521734</v>
       </c>
       <c r="I4">
-        <v>87.70725899999999</v>
+        <v>88.30223599999999</v>
       </c>
       <c r="J4" t="s">
         <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M4" t="s">
         <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O4">
-        <v>23.440923</v>
+        <v>22.521734</v>
       </c>
       <c r="P4">
-        <v>87.67574399999999</v>
+        <v>88.30223599999999</v>
       </c>
       <c r="Q4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R4">
-        <v>748.64</v>
+        <v>21.2</v>
       </c>
       <c r="S4">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -720,7 +729,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -728,8 +737,8 @@
       <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="F5">
-        <v>611</v>
+      <c r="F5" t="s">
+        <v>26</v>
       </c>
       <c r="G5" t="s">
         <v>29</v>
@@ -741,34 +750,34 @@
         <v>88.30223599999999</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K5">
-        <v>611</v>
+        <v>3</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" t="s">
         <v>22</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O5">
-        <v>22.521734</v>
+        <v>22.573481</v>
       </c>
       <c r="P5">
-        <v>88.30223599999999</v>
+        <v>88.23092200000001</v>
       </c>
       <c r="Q5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R5">
-        <v>391.48825</v>
+        <v>20</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>19.0827</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -779,7 +788,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -791,7 +800,7 @@
         <v>611</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H6">
         <v>22.521734</v>
@@ -800,329 +809,34 @@
         <v>88.30223599999999</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K6">
-        <v>611</v>
+        <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M6" t="s">
         <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O6">
-        <v>22.521734</v>
+        <v>22.573481</v>
       </c>
       <c r="P6">
-        <v>88.30223599999999</v>
+        <v>88.23092200000001</v>
       </c>
       <c r="Q6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="R6">
-        <v>391.48825</v>
+        <v>16</v>
       </c>
       <c r="S6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7">
-        <v>23.440923</v>
-      </c>
-      <c r="I7">
-        <v>87.67574399999999</v>
-      </c>
-      <c r="J7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-      <c r="L7" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7">
-        <v>23.50248767</v>
-      </c>
-      <c r="P7">
-        <v>87.73095685</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>34</v>
-      </c>
-      <c r="R7">
-        <v>748.64</v>
-      </c>
-      <c r="S7">
-        <v>11.2945</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>23.474314</v>
-      </c>
-      <c r="I8">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8">
-        <v>23.50248767</v>
-      </c>
-      <c r="P8">
-        <v>87.73095685</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>34</v>
-      </c>
-      <c r="R8">
-        <v>46.26</v>
-      </c>
-      <c r="S8">
-        <v>5.3613</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9">
-        <v>23.474314</v>
-      </c>
-      <c r="I9">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="J9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9">
-        <v>12</v>
-      </c>
-      <c r="L9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9">
-        <v>23.50248767</v>
-      </c>
-      <c r="P9">
-        <v>87.73095685</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>34</v>
-      </c>
-      <c r="R9">
-        <v>46.26</v>
-      </c>
-      <c r="S9">
-        <v>5.3613</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10">
-        <v>23.474314</v>
-      </c>
-      <c r="I10">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="J10" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10">
-        <v>23.474314</v>
-      </c>
-      <c r="P10">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10">
-        <v>46.26</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11">
-        <v>23.474314</v>
-      </c>
-      <c r="I11">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="J11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11">
-        <v>23.474314</v>
-      </c>
-      <c r="P11">
-        <v>87.70725899999999</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>33</v>
-      </c>
-      <c r="R11">
-        <v>46.26</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
+        <v>19.0827</v>
       </c>
     </row>
   </sheetData>
